--- a/artfynd/A 31263-2024 artfynd.xlsx
+++ b/artfynd/A 31263-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102229792</v>
+        <v>86101736</v>
       </c>
       <c r="B2" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -714,27 +709,31 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snickarängen, Vstm</t>
+          <t>Mossbo, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543279.1584434353</v>
+        <v>543187</v>
       </c>
       <c r="R2" t="n">
-        <v>6599728.277452854</v>
+        <v>6599961</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +752,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Himmeta</t>
+          <t>Kolsva</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +775,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ängsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -794,10 +788,227 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102229792</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Snickarängen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543279</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6599728</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Himmeta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Tina Nordberg, Kenneth Nordberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101634843</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mossbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543151</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599977</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tina Nordberg, Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31263-2024 artfynd.xlsx
+++ b/artfynd/A 31263-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86101736</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102229792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101634843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>